--- a/output/pdf_financials_xlsx/KEEK.xlsx
+++ b/output/pdf_financials_xlsx/KEEK.xlsx
@@ -5776,46 +5776,46 @@
         <v>1.514487</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>4.286142</v>
+        <v>4.365506</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>5.407155</v>
+        <v>6.316029</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>8.900447</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>13.010977</v>
+        <v>13.148612</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>16.998992</v>
+        <v>17.289942</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>18.991624</v>
+        <v>19.539722</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>20.572957</v>
+        <v>21.318568</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>21.67024</v>
+        <v>0.42036</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>1.629631</v>
+        <v>2.215575</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>2.603696</v>
+        <v>3.465941</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>2.137134</v>
+        <v>2.218989</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>1.908414</v>
+        <v>1.949214</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>1.948414</v>
+        <v>2.232993</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.940414</v>
+        <v>1.224993</v>
       </c>
       <c r="Q92" s="3" t="n">
         <v>0.860635</v>
@@ -10462,7 +10462,11 @@
           <t>Warrants reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12334,7 +12338,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -14128,7 +14136,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -15270,7 +15282,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -18276,7 +18292,11 @@
           <t>Warrants reserve (Note 9) 862,245</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -20770,7 +20790,11 @@
           <t>Warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -22416,7 +22440,11 @@
           <t>Warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -23660,7 +23688,11 @@
           <t>Warrants reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -24230,7 +24262,11 @@
           <t>Warrants reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -25094,7 +25130,11 @@
           <t>Warrants reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -26056,7 +26096,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -27382,7 +27426,11 @@
           <t>Share based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KEEK.xlsx
+++ b/output/pdf_financials_xlsx/KEEK.xlsx
@@ -1053,28 +1053,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.020955</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.048727</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004796</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006165</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022011</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.005423</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000411</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.070385</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.13745</v>
       </c>
     </row>
     <row r="13">
@@ -2084,16 +2084,16 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.684814</v>
+        <v>-5.662803</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-24.294181</v>
+        <v>-24.299604</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.897701</v>
+        <v>-3.898112</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.897701</v>
+        <v>-3.968086</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.164066</v>
@@ -2105,7 +2105,7 @@
         <v>2.678698</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.173621</v>
+        <v>-2.311071</v>
       </c>
     </row>
     <row r="28">
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.681272</v>
+        <v>-5.659261</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-24.206304</v>
+        <v>-24.211727</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.756095</v>
+        <v>-3.756506</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.714573</v>
+        <v>-3.784958</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.114217</v>
@@ -2231,7 +2231,7 @@
         <v>2.748868</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.136888</v>
+        <v>-2.274338</v>
       </c>
     </row>
     <row r="30">
@@ -2277,16 +2277,16 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-100.4035744152624</v>
+        <v>-100.0145800005514</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-327.6284523993211</v>
+        <v>-327.7018518368131</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-117.3829942094396</v>
+        <v>-117.3958385093362</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-96.7572564562612</v>
+        <v>-98.59064605330883</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-2.561224791836156</v>
@@ -2469,40 +2469,40 @@
         <v>24.406226</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.454476</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.754838</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.102659</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.943223</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.205761</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.09987799999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.087241</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.100155</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.031911</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.135473</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.03325</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.047412</v>
       </c>
     </row>
     <row r="35">
@@ -2579,40 +2579,40 @@
         <v>24.406226</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.454476</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.754838</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.102659</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.943223</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.1</v>
+        <v>0.305761</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.09987799999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.087241</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.100155</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.031911</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.135473</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.03325</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.047412</v>
       </c>
     </row>
     <row r="37">
@@ -3239,40 +3239,40 @@
         <v>0.497755</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.139354</v>
+        <v>0.684878</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.221196</v>
+        <v>0.466358</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.195434</v>
+        <v>0.092775</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.005868</v>
+        <v>0.06264500000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.8991209999999999</v>
+        <v>0.69336</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.209905</v>
+        <v>1.110027</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.928121</v>
+        <v>0.84088</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.50231</v>
+        <v>0.402155</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.441642</v>
+        <v>0.409731</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.5941959999999999</v>
+        <v>0.458723</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.014321</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.198457</v>
+        <v>0.151045</v>
       </c>
     </row>
     <row r="49">
@@ -7672,10 +7672,10 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.06453299999999999</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.069324</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7731,10 +7731,10 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.06453299999999999</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.069324</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -32234,7 +32234,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -61902,7 +61906,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -61988,7 +61992,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -62368,7 +62372,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -68416,7 +68420,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -72188,7 +72192,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -72288,7 +72292,7 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -82052,7 +82056,7 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -82150,7 +82154,7 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">

--- a/output/pdf_financials_xlsx/KEEK.xlsx
+++ b/output/pdf_financials_xlsx/KEEK.xlsx
@@ -874,16 +874,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7.823402</v>
+        <v>8.273137999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6.434774</v>
+        <v>7.033058</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>3.924556</v>
+        <v>4.426652</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>3.042567</v>
+        <v>3.164772</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0.050904</v>
@@ -6920,16 +6920,16 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.245069</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.07749399999999999</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -50968,7 +50968,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -53436,7 +53440,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -55640,7 +55648,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -57936,7 +57948,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -81594,7 +81610,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E768" t="inlineStr">
         <is>
           <t>-</t>
